--- a/data/merged/2026-09-23/MERGED_JP_Mite-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_JP_Mite-Vacuum_2026-09-23.xlsx
@@ -3371,13 +3371,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3415,13 +3415,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3465,7 +3465,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3509,7 +3509,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3679,13 +3679,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3723,13 +3723,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3943,13 +3943,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4031,13 +4031,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4169,7 +4169,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4207,7 +4207,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4295,13 +4295,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4471,13 +4471,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4559,13 +4559,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4653,7 +4653,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4741,7 +4741,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4867,13 +4867,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4999,13 +4999,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5043,13 +5043,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5198,314 +5198,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId43" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Product 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5847,7 +5539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6366,7 +6058,7 @@
       <c r="B3" s="11"/>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>B016UAX3VQ</t>
+          <t>B017SAF6OY</t>
         </is>
       </c>
       <c r="D3" s="12"/>
@@ -6379,23 +6071,23 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>松下 吸尘器 纸袋式 带室内灰尘探测传感器 粉色香槟 MC-DF500G-P</t>
+          <t>Aiwa 花粉・螨虫去除 被褥专用喷嘴 花粉&amp;螨虫清洁器 日本制造</t>
         </is>
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B016UAX3VQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B017SAF6OY?psc=1</t>
         </is>
       </c>
       <c r="K3" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51CMS9l84gL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61dODBedyYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>B016UAX3VQ</t>
+          <t>B017SAF6OY</t>
         </is>
       </c>
       <c r="M3" s="1"/>
@@ -6411,16 +6103,18 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3"/>
-      <c r="Z3" s="13"/>
+      <c r="Z3" s="13">
+        <v>10</v>
+      </c>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3" s="17">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="AE3"/>
       <c r="AF3" s="18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AG3" s="19">
         <v>0</v>
@@ -6472,7 +6166,7 @@
       <c r="B4" s="11"/>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>B017SAF6OY</t>
+          <t>B01GUPMJMA</t>
         </is>
       </c>
       <c r="D4" s="12"/>
@@ -6485,23 +6179,23 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>Aiwa 花粉・螨虫去除 被褥专用喷嘴 花粉&amp;螨虫清洁器 日本制造</t>
+          <t>IRIS OHYAMA 超吸引 被褥吸尘器 白色 IC-FAC2</t>
         </is>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B017SAF6OY?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61dODBedyYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51kQ4uomOdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>B017SAF6OY</t>
+          <t>B01GUPMJMA</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -6517,18 +6211,16 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4"/>
-      <c r="Z4" s="13">
-        <v>10</v>
-      </c>
+      <c r="Z4" s="13"/>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4" s="17">
-        <v>121</v>
+        <v>1901</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" s="18">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AG4" s="19">
         <v>0</v>
@@ -6580,7 +6272,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>B01GUPMJMA</t>
+          <t>B07H4MYMP9</t>
         </is>
       </c>
       <c r="D5" s="12"/>
@@ -6593,23 +6285,23 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 超吸引 被褥吸尘器 白色 IC-FAC2</t>
+          <t>[防螨] IRIS OHYAMA(IRIS OHYAMA) 被褥清洁剂 白色 防螨 拍头约 5,800 次/分钟 热空气功能 带过滤网 IC-FAC2</t>
         </is>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07H4MYMP9?psc=1</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51kQ4uomOdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41W46tl8-UL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>B01GUPMJMA</t>
+          <t>B07H4MYMP9</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -6625,12 +6317,14 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5"/>
-      <c r="Z5" s="13"/>
+      <c r="Z5" s="13">
+        <v>51</v>
+      </c>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="17">
-        <v>1901</v>
+        <v>4482</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="18">
@@ -6686,7 +6380,7 @@
       <c r="B6" s="11"/>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>B07H4MYMP9</t>
+          <t>B07RT2QD4C</t>
         </is>
       </c>
       <c r="D6" s="12"/>
@@ -6699,23 +6393,23 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>[防螨] IRIS OHYAMA(IRIS OHYAMA) 被褥清洁剂 白色 防螨 拍头约 5,800 次/分钟 热空气功能 带过滤网 IC-FAC2</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 全国适用(电源 AC100V 50/60hz) 手持式 强力 被褥清洁器 搭载螨虫和簸箕 拍打 约6,500次/分钟 IC-FAC3</t>
         </is>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07H4MYMP9?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41W46tl8-UL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>B07H4MYMP9</t>
+          <t>B07RT2QD4C</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -6731,14 +6425,12 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6"/>
-      <c r="Z6" s="13">
-        <v>51</v>
-      </c>
+      <c r="Z6" s="13"/>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="17">
-        <v>4482</v>
+        <v>2511</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="18">
@@ -6794,7 +6486,7 @@
       <c r="B7" s="11"/>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>B07RT2QD4C</t>
+          <t>B08XM26HKK</t>
         </is>
       </c>
       <c r="D7" s="12"/>
@@ -6807,23 +6499,23 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 全国适用(电源 AC100V 50/60hz) 手持式 强力 被褥清洁器 搭载螨虫和簸箕 拍打 约6,500次/分钟 IC-FAC3</t>
+          <t>Raycop 被子清洁剂 UV除菌 吸力 强力拍打 搭载光清洁机制" 病毒/室内灰尘 轻量 小巧 RE-100JWH-E 白色</t>
         </is>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XM26HKK?psc=1</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>B07RT2QD4C</t>
+          <t>B08XM26HKK</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -6844,7 +6536,7 @@
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="17">
-        <v>2511</v>
+        <v>326</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="18">
@@ -6900,7 +6592,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>B08XM26HKK</t>
+          <t>B09JFPJWRW</t>
         </is>
       </c>
       <c r="D8" s="12"/>
@@ -6913,23 +6605,23 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Raycop 被子清洁剂 UV除菌 吸力 强力拍打 搭载光清洁机制" 病毒/室内灰尘 轻量 小巧 RE-100JWH-E 白色</t>
+          <t>Raycop 雷水杯 UV 无线 被褥清洁剂 除螨病毒 UV除菌 1.4千克 超轻 独立收纳 最长可使用120分钟 强力拍打 防螨 RAYCOP 被褥吸尘器</t>
         </is>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08XM26HKK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>B08XM26HKK</t>
+          <t>B09JFPJWRW</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6950,11 +6642,11 @@
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="17">
-        <v>326</v>
+        <v>490</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="18">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG8" s="19">
         <v>0</v>
@@ -7006,7 +6698,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>B09JFPJWRW</t>
+          <t>B09WMDJ3R8</t>
         </is>
       </c>
       <c r="D9" s="12"/>
@@ -7019,23 +6711,23 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Raycop 雷水杯 UV 无线 被褥清洁剂 除螨病毒 UV除菌 1.4千克 超轻 独立收纳 最长可使用120分钟 强力拍打 防螨 RAYCOP 被褥吸尘器</t>
+          <t>RAYCOP UV被褥清洁剂 VCEN-100 UV99.9%除菌 除病毒 杀死螨虫 拍打18,000次 (白色) 防螨</t>
         </is>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71xsLoIIE2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>B09JFPJWRW</t>
+          <t>B09WMDJ3R8</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7056,11 +6748,11 @@
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="17">
-        <v>490</v>
+        <v>45</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG9" s="19">
         <v>0</v>
@@ -7112,7 +6804,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>B09WMDJ3R8</t>
+          <t>B0BBVFX2GR</t>
         </is>
       </c>
       <c r="D10" s="12"/>
@@ -7125,23 +6817,23 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>RAYCOP UV被褥清洁剂 VCEN-100 UV99.9%除菌 除病毒 杀死螨虫 拍打18,000次 (白色) 防螨</t>
+          <t>爱丽思欧雅玛(IRIS OHYAMA) 布団清洁器 配有螨虫和灰尘传感器 拍打 约6,500转/分 FCA-13-C 象牙色</t>
         </is>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0BBVFX2GR?psc=1</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71xsLoIIE2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41yNLrDa+RL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>B09WMDJ3R8</t>
+          <t>B0BBVFX2GR</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7162,11 +6854,11 @@
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="17">
-        <v>45</v>
+        <v>432</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG10" s="19">
         <v>0</v>
@@ -7218,7 +6910,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>B0BBVFX2GR</t>
+          <t>B0BCDMQGQ9</t>
         </is>
       </c>
       <c r="D11" s="12"/>
@@ -7231,23 +6923,23 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>爱丽思欧雅玛(IRIS OHYAMA) 布団清洁器 配有螨虫和灰尘传感器 拍打 约6,500转/分 FCA-13-C 象牙色</t>
+          <t>鸢尾 Ohyama 高功率被褥清洁器 鸢尾 Ohyama 史上最强型号 敲打次数/每分钟约15,000次 超高速振动 白色 FCA-B2H-W</t>
         </is>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BBVFX2GR?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0BCDMQGQ9?psc=1</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41yNLrDa+RL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41hvEdYzqRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>B0BBVFX2GR</t>
+          <t>B0BCDMQGQ9</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7268,7 +6960,7 @@
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="17">
-        <v>432</v>
+        <v>23</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="18">
@@ -7324,7 +7016,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>B0BCDMQGQ9</t>
+          <t>B0BCF1JPCL</t>
         </is>
       </c>
       <c r="D12" s="12"/>
@@ -7337,23 +7029,23 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>鸢尾 Ohyama 高功率被褥清洁器 鸢尾 Ohyama 史上最强型号 敲打次数/每分钟约15,000次 超高速振动 白色 FCA-B2H-W</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥吸尘器 拍打次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A</t>
         </is>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BCDMQGQ9?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41hvEdYzqRL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>B0BCDMQGQ9</t>
+          <t>B0BCF1JPCL</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7374,11 +7066,11 @@
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="17">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="18">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AG12" s="19">
         <v>0</v>
@@ -7430,7 +7122,7 @@
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>B0BCF1JPCL</t>
+          <t>B0CRYZV8CQ</t>
         </is>
       </c>
       <c r="D13" s="12"/>
@@ -7443,23 +7135,23 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥吸尘器 拍打次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A</t>
+          <t>Jimmy 被子清洁器 专用被子清洁机 螨虫清洁机 床上清洁机 螨虫灰尘传感器 被子拍打 UV除菌 16Kpa 480w超高速拍打 超吸引 60度温风功能 花粉 螨虫防治 螨虫驱除 室内灰尘 地毯 床 梅雨 (BX7 Pro)</t>
         </is>
       </c>
       <c r="I13" s="12"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>B0BCF1JPCL</t>
+          <t>B0CRYZV8CQ</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7480,11 +7172,11 @@
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="17">
-        <v>5</v>
+        <v>165</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="18">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AG13" s="19">
         <v>0</v>
@@ -7536,7 +7228,7 @@
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>B0CRYZV8CQ</t>
+          <t>B0CZN7FLSN</t>
         </is>
       </c>
       <c r="D14" s="12"/>
@@ -7549,23 +7241,23 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Jimmy 被子清洁器 专用被子清洁机 螨虫清洁机 床上清洁机 螨虫灰尘传感器 被子拍打 UV除菌 16Kpa 480w超高速拍打 超吸引 60度温风功能 花粉 螨虫防治 螨虫驱除 室内灰尘 地毯 床 梅雨 (BX7 Pro)</t>
+          <t>JIMMY JV35 被褥清洁剂 宠物防护螨去除大师s480W 强力吸力、超宽吸嘴,头发的吸入量可提高 130% 60℃ 的暖风 HEPA 过滤器 0.5L 大容量防尘杯 螨吸尘器 过敏原、花粉、室内尘螨 床 沙发 地毯 雨季</t>
         </is>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CZN7FLSN?psc=1</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61gx54pmm0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>B0CRYZV8CQ</t>
+          <t>B0CZN7FLSN</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7586,11 +7278,11 @@
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="17">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG14" s="19">
         <v>0</v>
@@ -7642,7 +7334,7 @@
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>B0CZN7FLSN</t>
+          <t>B0D1XQPH2V</t>
         </is>
       </c>
       <c r="D15" s="12"/>
@@ -7655,23 +7347,23 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>JIMMY JV35 被褥清洁剂 宠物防护螨去除大师s480W 强力吸力、超宽吸嘴,头发的吸入量可提高 130% 60℃ 的暖风 HEPA 过滤器 0.5L 大容量防尘杯 螨吸尘器 过敏原、花粉、室内尘螨 床 沙发 地毯 雨季</t>
+          <t>JIGOO J300 被褥吸尘器 除螨过滤器分离设计s500W 蒲团吸尘器 13kpa 强吸力 除病毒 紫外线除菌 防过敏原 55℃加热 热风干燥 被褥吸尘器</t>
         </is>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CZN7FLSN?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61gx54pmm0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/81kvopazcOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>B0CZN7FLSN</t>
+          <t>B0D1XQPH2V</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7692,11 +7384,11 @@
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="17">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG15" s="19">
         <v>0</v>
@@ -7748,7 +7440,7 @@
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>B0D1XQPH2V</t>
+          <t>B0D7C6VH4G</t>
         </is>
       </c>
       <c r="D16" s="12"/>
@@ -7761,23 +7453,23 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>JIGOO J300 被褥吸尘器 除螨过滤器分离设计s500W 蒲团吸尘器 13kpa 强吸力 除病毒 紫外线除菌 防过敏原 55℃加热 热风干燥 被褥吸尘器</t>
+          <t>UWANT 被褥清洁器 具有13Kpa的强力吸力 每分钟36,000次的自攻功能有效去除床、沙发、地毯上的螨虫和灰尘 M100 橙与白</t>
         </is>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D7C6VH4G?psc=1</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/81kvopazcOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71b-Rog4TuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>B0D1XQPH2V</t>
+          <t>B0D7C6VH4G</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7798,11 +7490,11 @@
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="17">
-        <v>109</v>
+        <v>309</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG16" s="19">
         <v>0</v>
@@ -7854,7 +7546,7 @@
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>B0D7C6VH4G</t>
+          <t>B0D7HWNDXS</t>
         </is>
       </c>
       <c r="D17" s="12"/>
@@ -7867,23 +7559,23 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>UWANT 被褥清洁器 具有13Kpa的强力吸力 每分钟36,000次的自攻功能有效去除床、沙发、地毯上的螨虫和灰尘 M100 橙与白</t>
+          <t>EFSHREE 布団掃除機 布団清洁机 除螨清洁机 布団干燥机 UV灯 HEPA滤网 温风 10000Pa 超轻1.25千克 适用花粉 床 沙发 家用车载 (白色)</t>
         </is>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D7C6VH4G?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71b-Rog4TuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/6147nu3B4yL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>B0D7C6VH4G</t>
+          <t>B0D7HWNDXS</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7904,11 +7596,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="17">
-        <v>309</v>
+        <v>83</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="18">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AG17" s="19">
         <v>0</v>
@@ -7960,7 +7652,7 @@
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>B0D7HWNDXS</t>
+          <t>B0DGTN1LGP</t>
         </is>
       </c>
       <c r="D18" s="12"/>
@@ -7973,23 +7665,23 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>EFSHREE 布団掃除機 布団清洁机 除螨清洁机 布団干燥机 UV灯 HEPA滤网 温风 10000Pa 超轻1.25千克 适用花粉 床 沙发 家用车载 (白色)</t>
+          <t>Jimmy 被子清洁器 被子用吸尘器 螨虫清除吸尘器 床上清洁器 螨虫灰尘传感器 被子拍打 UV消毒 15Kpa 500w超高速拍打 超吸力 65度温风功能 花粉 螨虫防护 螨虫驱除 室内灰尘 地毯 床 梅雨（WB81）</t>
         </is>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/6147nu3B4yL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>B0D7HWNDXS</t>
+          <t>B0DGTN1LGP</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8010,11 +7702,11 @@
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="17">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AG18" s="19">
         <v>0</v>
@@ -8066,7 +7758,7 @@
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>B0DGTN1LGP</t>
+          <t>B0DH8B8TM4</t>
         </is>
       </c>
       <c r="D19" s="12"/>
@@ -8079,23 +7771,23 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Jimmy 被子清洁器 被子用吸尘器 螨虫清除吸尘器 床上清洁器 螨虫灰尘传感器 被子拍打 UV消毒 15Kpa 500w超高速拍打 超吸力 65度温风功能 花粉 螨虫防护 螨虫驱除 室内灰尘 地毯 床 梅雨（WB81）</t>
+          <t>螨虫吸尘器 蒲团吸尘器 小型吸尘器 被褥吸尘器 附带2个刷头 USB 充电式 手持式 手持式 无线・便携・除螨器 轻巧极简外观 家庭协调</t>
         </is>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>B0DGTN1LGP</t>
+          <t>B0DH8B8TM4</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8115,13 +7807,9 @@
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
-      <c r="AD19" s="17">
-        <v>57</v>
-      </c>
+      <c r="AD19" s="17"/>
       <c r="AE19"/>
-      <c r="AF19" s="18">
-        <v>4</v>
-      </c>
+      <c r="AF19" s="18"/>
       <c r="AG19" s="19">
         <v>0</v>
       </c>
@@ -8172,7 +7860,7 @@
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>B0DH8B8TM4</t>
+          <t>B0DJ84X2K4</t>
         </is>
       </c>
       <c r="D20" s="12"/>
@@ -8185,23 +7873,23 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>螨虫吸尘器 蒲团吸尘器 小型吸尘器 被褥吸尘器 附带2个刷头 USB 充电式 手持式 手持式 无线・便携・除螨器 轻巧极简外观 家庭协调</t>
+          <t>AQUA 被褥清洁器(拍打28,800次 / UV除菌) 高端 双刷(螨虫/室内尘/花粉) 被褥吸尘器 可水洗CF10WR</t>
         </is>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DJ84X2K4?psc=1</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61lNaH-6QjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>B0DH8B8TM4</t>
+          <t>B0DJ84X2K4</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8217,13 +7905,19 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20"/>
-      <c r="Z20" s="13"/>
+      <c r="Z20" s="13">
+        <v>111</v>
+      </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
-      <c r="AD20" s="17"/>
+      <c r="AD20" s="17">
+        <v>4</v>
+      </c>
       <c r="AE20"/>
-      <c r="AF20" s="18"/>
+      <c r="AF20" s="18">
+        <v>4.8</v>
+      </c>
       <c r="AG20" s="19">
         <v>0</v>
       </c>
@@ -8274,7 +7968,7 @@
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>B0DJ84X2K4</t>
+          <t>B0DJ8MNLKW</t>
         </is>
       </c>
       <c r="D21" s="12"/>
@@ -8287,23 +7981,23 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>AQUA 被褥清洁器(拍打28,800次 / UV除菌) 高端 双刷(螨虫/室内尘/花粉) 被褥吸尘器 可水洗CF10WR</t>
+          <t>Raycop 雷杯 UV 无线 被褥清洁剂 RJS2 UV除菌 螨虫 屋尘埃 病毒99.9% 去除 强力吸力 HEPA过滤器 RAYCOP 被褥吸尘器 自立收纳</t>
         </is>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DJ84X2K4?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DJ8MNLKW?psc=1</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61lNaH-6QjL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61hr6UbLVxL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>B0DJ84X2K4</t>
+          <t>B0DJ8MNLKW</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8319,18 +8013,16 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21"/>
-      <c r="Z21" s="13">
-        <v>111</v>
-      </c>
+      <c r="Z21" s="13"/>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="17">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="18">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AG21" s="19">
         <v>0</v>
@@ -8382,7 +8074,7 @@
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>B0DJ8MNLKW</t>
+          <t>B0DP629CCF</t>
         </is>
       </c>
       <c r="D22" s="12"/>
@@ -8395,23 +8087,23 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Raycop 雷杯 UV 无线 被褥清洁剂 RJS2 UV除菌 螨虫 屋尘埃 病毒99.9% 去除 强力吸力 HEPA过滤器 RAYCOP 被褥吸尘器 自立收纳</t>
+          <t>小米床垫清洁器 12,000次高频振动 UV光线99%消毒 螨虫清除 12,000帕吸力 50℃温风干燥 毛发、垃圾、灰尘清除 旋风式四层过滤 可清洗 1.63kg轻量设计s高周波振動 UVライト 12,000Paの吸引力 軽量設計 4層洗浄可能</t>
         </is>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DJ8MNLKW?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DP629CCF?psc=1</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61hr6UbLVxL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61YqmCRO62L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>B0DJ8MNLKW</t>
+          <t>B0DP629CCF</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8432,11 +8124,11 @@
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="17">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG22" s="19">
         <v>0</v>
@@ -8488,7 +8180,7 @@
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>B0DP629CCF</t>
+          <t>B0DQPZRS8L</t>
         </is>
       </c>
       <c r="D23" s="12"/>
@@ -8501,23 +8193,23 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>小米床垫清洁器 12,000次高频振动 UV光线99%消毒 螨虫清除 12,000帕吸力 50℃温风干燥 毛发、垃圾、灰尘清除 旋风式四层过滤 可清洗 1.63kg轻量设计s高周波振動 UVライト 12,000Paの吸引力 軽量設計 4層洗浄可能</t>
+          <t>被褥吸尘器 被褥吸尘器 无线 18KPa强力吸力 Linkifly MT1 HEPA过滤器 LED显示屏 35分钟长时间运行s超高速拍打约 80000 次/分钟,强吸力,双杯过滤设计,Type-C 充电,超轻低噪音,螨虫对策,花粉和房屋灰尘,防过</t>
         </is>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DP629CCF?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DQPZRS8L?psc=1</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61YqmCRO62L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/612s3TGcUVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>B0DP629CCF</t>
+          <t>B0DQPZRS8L</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8538,11 +8230,11 @@
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="17">
-        <v>75</v>
+        <v>1014</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG23" s="19">
         <v>0</v>
@@ -8594,7 +8286,7 @@
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>B0DQPZRS8L</t>
+          <t>B0DR1YK9LS</t>
         </is>
       </c>
       <c r="D24" s="12"/>
@@ -8607,23 +8299,23 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>被褥吸尘器 被褥吸尘器 无线 18KPa强力吸力 Linkifly MT1 HEPA过滤器 LED显示屏 35分钟长时间运行s超高速拍打约 80000 次/分钟,强吸力,双杯过滤设计,Type-C 充电,超轻低噪音,螨虫对策,花粉和房屋灰尘,防过</t>
+          <t>床垫清洁器 床垫吸尘器 无线 1.2kg超轻量 UV杀菌 18Kpa 强力拍打 紧凑 病毒去除 螨虫驱除 床垫 清洁 地毯 床 花粉 螨虫防护 梅雨季节防护 螨虫清洁吸尘器 エコジー</t>
         </is>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DQPZRS8L?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/612s3TGcUVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>B0DQPZRS8L</t>
+          <t>B0DR1YK9LS</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8644,11 +8336,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="17">
-        <v>1014</v>
+        <v>100</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="18">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AG24" s="19">
         <v>0</v>
@@ -8700,7 +8392,7 @@
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>B0DR1YK9LS</t>
+          <t>B0DSVXKTTZ</t>
         </is>
       </c>
       <c r="D25" s="12"/>
@@ -8713,23 +8405,23 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>床垫清洁器 床垫吸尘器 无线 1.2kg超轻量 UV杀菌 18Kpa 强力拍打 紧凑 病毒去除 螨虫驱除 床垫 清洁 地毯 床 花粉 螨虫防护 梅雨季节防护 螨虫清洁吸尘器 エコジー</t>
+          <t>CREATULIZE被褥吸尘器 强力吸力UV除菌55℃高热技术,HEPA过滤 床垫、地板、沙发、地毯、宠物毛使用 吸尘器</t>
         </is>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DSVXKTTZ?psc=1</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/715CyXTopOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>B0DR1YK9LS</t>
+          <t>B0DSVXKTTZ</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8750,11 +8442,11 @@
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="17">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="18">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AG25" s="19">
         <v>0</v>
@@ -8806,7 +8498,7 @@
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>B0DSVXKTTZ</t>
+          <t>B0DW45FNFD</t>
         </is>
       </c>
       <c r="D26" s="12"/>
@@ -8819,23 +8511,23 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>CREATULIZE被褥吸尘器 强力吸力UV除菌55℃高热技术,HEPA过滤 床垫、地板、沙发、地毯、宠物毛使用 吸尘器</t>
+          <t>JIGOO S100 被褥吸尘器 被褥 吸尘器 防螨 55°C热风干UV除菌12KPa强力吸力高速拍打震动螨虫 螨虫过滤网分离设计 0.38L大容量防尘杯 可水洗 230mm超宽吸嘴 1.3kg超轻量 螨传感器 LED显示屏 床垫、床、沙发、地毯、宠</t>
         </is>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DSVXKTTZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/715CyXTopOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71332p8jV1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>B0DSVXKTTZ</t>
+          <t>B0DW45FNFD</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8856,11 +8548,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="17">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="18">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG26" s="19">
         <v>0</v>
@@ -8912,7 +8604,7 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B0DW45FNFD</t>
+          <t>B0DZCG5HCH</t>
         </is>
       </c>
       <c r="D27" s="12"/>
@@ -8925,23 +8617,23 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>JIGOO S100 被褥吸尘器 被褥 吸尘器 防螨 55°C热风干UV除菌12KPa强力吸力高速拍打震动螨虫 螨虫过滤网分离设计 0.38L大容量防尘杯 可水洗 230mm超宽吸嘴 1.3kg超轻量 螨传感器 LED显示屏 床垫、床、沙发、地毯、宠</t>
+          <t>Jimmy Jimy BX8 被褥吸尘器 被子吸尘器 手持式 500W 15kPa强力吸力 65℃ 被褥干燥 负离子 超声波 UV除菌s240 毫米吸嘴 HEPA 过滤器螨传感器 0.5L 大容量超快拍除尘除尘螨驱除宠物毛发、花粉、过敏原兼容床垫</t>
         </is>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DZCG5HCH?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71332p8jV1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71hIr36PswL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B0DW45FNFD</t>
+          <t>B0DZCG5HCH</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -8962,11 +8654,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="17">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG27" s="19">
         <v>0</v>
@@ -9018,7 +8710,7 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B0DY61ZS3S</t>
+          <t>B0F2MJH8GH</t>
         </is>
       </c>
       <c r="D28" s="12"/>
@@ -9031,23 +8723,23 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>戴森 原装 戴森 Fton 工具2 500 [平行进口商品]</t>
+          <t>KEEPJOY 布団清洁器 被子吸尘器 床垫清洁器 螨虫清除 配备螨虫灰尘传感器 12000RPM 拍打振动 65℃热风功能 UV灯消毒 HEPA滤网 病毒清除 0.6L大容量 适用于被子 床垫 沙发 地毯 舒适的睡眠体验 花粉季节 梅雨季节 AC1</t>
         </is>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DY61ZS3S?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0F2MJH8GH?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31dizVJn3lL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71Gz6T9kaVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B0DY61ZS3S</t>
+          <t>B0F2MJH8GH</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9068,11 +8760,11 @@
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="17">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="18">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="AG28" s="19">
         <v>0</v>
@@ -9124,7 +8816,7 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B0DZCG5HCH</t>
+          <t>B0F2MLKF9S</t>
         </is>
       </c>
       <c r="D29" s="12"/>
@@ -9137,23 +8829,23 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Jimmy Jimy BX8 被褥吸尘器 被子吸尘器 手持式 500W 15kPa强力吸力 65℃ 被褥干燥 负离子 超声波 UV除菌s240 毫米吸嘴 HEPA 过滤器螨传感器 0.5L 大容量超快拍除尘除尘螨驱除宠物毛发、花粉、过敏原兼容床垫</t>
+          <t>KEEPJOY 被褥吸尘器 无绳 13Kpa 超 被褥吸尘器 搭载螨虫感应器 震动65℃温风功能 UV灯除菌 超声波 HEPA过滤器 99.9% 去除 双杯 分离设计 0.6L大容量集尘 可整体清洗 一键开启 被褥 床垫 沙发 地毯 舒适睡眠 花粉季</t>
         </is>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DZCG5HCH?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0F2MLKF9S?psc=1</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71hIr36PswL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/7194c3NEgeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>B0DZCG5HCH</t>
+          <t>B0F2MLKF9S</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9174,11 +8866,11 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="17">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="18">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AG29" s="19">
         <v>0</v>
@@ -9230,7 +8922,7 @@
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>B0F2MJH8GH</t>
+          <t>B0F4WKGDNF</t>
         </is>
       </c>
       <c r="D30" s="12"/>
@@ -9243,23 +8935,23 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>KEEPJOY 布団清洁器 被子吸尘器 床垫清洁器 螨虫清除 配备螨虫灰尘传感器 12000RPM 拍打振动 65℃热风功能 UV灯消毒 HEPA滤网 病毒清除 0.6L大容量 适用于被子 床垫 沙发 地毯 舒适的睡眠体验 花粉季节 梅雨季节 AC1</t>
+          <t>HAUSHOF 被褥吸尘器 被褥吸尘器 螨虫 吸尘器 防螨 UV除菌 无线 60000次/分钟高速敲打 HEPA过滤网 被褥 床 沙发 地毯 靠垫 毛/垃圾/除尘 1.4kg轻量化</t>
         </is>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0F2MJH8GH?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71Gz6T9kaVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B0F2MJH8GH</t>
+          <t>B0F4WKGDNF</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9280,11 +8972,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="17">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="18">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG30" s="19">
         <v>0</v>
@@ -9336,7 +9028,7 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B0F2MLKF9S</t>
+          <t>B0FB3663JX</t>
         </is>
       </c>
       <c r="D31" s="12"/>
@@ -9349,23 +9041,23 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>KEEPJOY 被褥吸尘器 无绳 13Kpa 超 被褥吸尘器 搭载螨虫感应器 震动65℃温风功能 UV灯除菌 超声波 HEPA过滤器 99.9% 去除 双杯 分离设计 0.6L大容量集尘 可整体清洗 一键开启 被褥 床垫 沙发 地毯 舒适睡眠 花粉季</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥吸尘器 搭载去毛功能 大功率 灰尘感应传感器 热风功能 易于清洁FCA-31PZ1-W 白色</t>
         </is>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0F2MLKF9S?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FB3663JX?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/7194c3NEgeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51kxnq4fNYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B0F2MLKF9S</t>
+          <t>B0FB3663JX</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9381,16 +9073,18 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31"/>
-      <c r="Z31" s="13"/>
+      <c r="Z31" s="13">
+        <v>76</v>
+      </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="17">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="18">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG31" s="19">
         <v>0</v>
@@ -9442,7 +9136,7 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B0F4WKGDNF</t>
+          <t>B0FCBS5DCM</t>
         </is>
       </c>
       <c r="D32" s="12"/>
@@ -9455,23 +9149,23 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF 被褥吸尘器 被褥吸尘器 螨虫 吸尘器 防螨 UV除菌 无线 60000次/分钟高速敲打 HEPA过滤网 被褥 床 沙发 地毯 靠垫 毛/垃圾/除尘 1.4kg轻量化</t>
+          <t>UWANT M600 被褥清洁剂</t>
         </is>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FCBS5DCM?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71sM4fI8XJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B0F4WKGDNF</t>
+          <t>B0FCBS5DCM</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9492,11 +9186,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="17">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="18">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG32" s="19">
         <v>0</v>
@@ -9548,7 +9242,7 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B0FB3663JX</t>
+          <t>B0FR16C82Q</t>
         </is>
       </c>
       <c r="D33" s="12"/>
@@ -9561,23 +9255,23 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥吸尘器 搭载去毛功能 大功率 灰尘感应传感器 热风功能 易于清洁FCA-31PZ1-W 白色</t>
+          <t>CokBlu 被褥清洁剂 除螨器 强力吸力 USB 充电式 小型吸尘器 去除灰尘、花粉 附带保护板 易于清洁 轻巧便携 时尚 人气款 多功能 适用于床、沙发、汽车、办公室 家庭、商业用途 适合搬家贺礼</t>
         </is>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FB3663JX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FR16C82Q?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51kxnq4fNYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51dSYaVLTcL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B0FB3663JX</t>
+          <t>B0FR16C82Q</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9593,19 +9287,13 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33"/>
-      <c r="Z33" s="13">
-        <v>76</v>
-      </c>
+      <c r="Z33" s="13"/>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
-      <c r="AD33" s="17">
-        <v>32</v>
-      </c>
+      <c r="AD33" s="17"/>
       <c r="AE33"/>
-      <c r="AF33" s="18">
-        <v>4.3</v>
-      </c>
+      <c r="AF33" s="18"/>
       <c r="AG33" s="19">
         <v>0</v>
       </c>
@@ -9656,7 +9344,7 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B0FCBS5DCM</t>
+          <t>B0FR467QTB</t>
         </is>
       </c>
       <c r="D34" s="12"/>
@@ -9669,23 +9357,23 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>UWANT M600 被褥清洁剂</t>
+          <t>【强力除螨工具套装】IRIS OHYAMA 被褥干燥机 被褥清洁器套装 除螨 FK-EC2 IC-FAC2</t>
         </is>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FCBS5DCM?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FR467QTB?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71sM4fI8XJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/31KvYyBRXvL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B0FCBS5DCM</t>
+          <t>B0FR467QTB</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9701,17 +9389,15 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34"/>
-      <c r="Z34" s="13"/>
+      <c r="Z34" s="13">
+        <v>120</v>
+      </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
-      <c r="AD34" s="17">
-        <v>95</v>
-      </c>
+      <c r="AD34" s="17"/>
       <c r="AE34"/>
-      <c r="AF34" s="18">
-        <v>4.5</v>
-      </c>
+      <c r="AF34" s="18"/>
       <c r="AG34" s="19">
         <v>0</v>
       </c>
@@ -9762,7 +9448,7 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0FR16C82Q</t>
+          <t>B0FWBY3CVW</t>
         </is>
       </c>
       <c r="D35" s="12"/>
@@ -9775,23 +9461,23 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>CokBlu 被褥清洁剂 除螨器 强力吸力 USB 充电式 小型吸尘器 去除灰尘、花粉 附带保护板 易于清洁 轻巧便携 时尚 人气款 多功能 适用于床、沙发、汽车、办公室 家庭、商业用途 适合搬家贺礼</t>
+          <t>被褥吸尘器 无线 UV除菌 18Kpa 1.2千克 超轻 小巧 被褥吸尘器s分离式充电支架 90,000 次/分钟强力拍除病毒去除螨虫花粉螨对策雨季对策长寿命床垫清洁地毯床</t>
         </is>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FR16C82Q?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FWBY3CVW?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51dSYaVLTcL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71d9mh-B3OL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0FR16C82Q</t>
+          <t>B0FWBY3CVW</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9811,9 +9497,13 @@
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
-      <c r="AD35" s="17"/>
+      <c r="AD35" s="17">
+        <v>41</v>
+      </c>
       <c r="AE35"/>
-      <c r="AF35" s="18"/>
+      <c r="AF35" s="18">
+        <v>4.4</v>
+      </c>
       <c r="AG35" s="19">
         <v>0</v>
       </c>
@@ -9864,7 +9554,7 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0FR467QTB</t>
+          <t>B0G1C3LTTM</t>
         </is>
       </c>
       <c r="D36" s="12"/>
@@ -9877,23 +9567,23 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>【强力除螨工具套装】IRIS OHYAMA 被褥干燥机 被褥清洁器套装 除螨 FK-EC2 IC-FAC2</t>
+          <t>布団清洁器 被褥吸尘器 螨虫去除机 螨虫吸尘器 地毯清洁器 静音 高功率 强力吸引 轻量 螨虫 花粉 室内灰尘 被褥 清洁 无绳 TVC002-PU KOMFLORA</t>
         </is>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FR467QTB?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G1C3LTTM?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31KvYyBRXvL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51MPPMKoAmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0FR467QTB</t>
+          <t>B0G1C3LTTM</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9909,15 +9599,17 @@
       <c r="W36" s="13"/>
       <c r="X36" s="13"/>
       <c r="Y36"/>
-      <c r="Z36" s="13">
-        <v>120</v>
-      </c>
+      <c r="Z36" s="13"/>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36"/>
-      <c r="AD36" s="17"/>
+      <c r="AD36" s="17">
+        <v>15</v>
+      </c>
       <c r="AE36"/>
-      <c r="AF36" s="18"/>
+      <c r="AF36" s="18">
+        <v>4.5</v>
+      </c>
       <c r="AG36" s="19">
         <v>0</v>
       </c>
@@ -9968,7 +9660,7 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0FWBY3CVW</t>
+          <t>B0G5PQCR4W</t>
         </is>
       </c>
       <c r="D37" s="12"/>
@@ -9981,23 +9673,23 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>被褥吸尘器 无线 UV除菌 18Kpa 1.2千克 超轻 小巧 被褥吸尘器s分离式充电支架 90,000 次/分钟强力拍除病毒去除螨虫花粉螨对策雨季对策长寿命床垫清洁地毯床</t>
+          <t>Airpher 褥子清洁剂 UV除菌、除螨、病毒 最大18Kpa 强力吸&amp;拍打40800次 500Ws配备 2 个阶段的 HEPA 过滤器,过敏原对策 (16,000 Pa),低模式 (16,000Pa),低模式 (16,000Pa),超声波技术</t>
         </is>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FWBY3CVW?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G5PQCR4W?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71d9mh-B3OL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71Bp3OKbP4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B0FWBY3CVW</t>
+          <t>B0G5PQCR4W</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10018,11 +9710,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="17">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG37" s="19">
         <v>0</v>
@@ -10074,7 +9766,7 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0G1C3LTTM</t>
+          <t>B0G8CZQYDB</t>
         </is>
       </c>
       <c r="D38" s="12"/>
@@ -10087,23 +9779,23 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>布団清洁器 被褥吸尘器 螨虫去除机 螨虫吸尘器 地毯清洁器 静音 高功率 强力吸引 轻量 螨虫 花粉 室内灰尘 被褥 清洁 无绳 TVC002-PU KOMFLORA</t>
+          <t>被褥清洁剂 大功率 防螨 宽头 拍打 约14000次/分钟 FCA-22H-C 象牙色</t>
         </is>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G1C3LTTM?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51MPPMKoAmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0G1C3LTTM</t>
+          <t>B0G8CZQYDB</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10123,13 +9815,9 @@
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
-      <c r="AD38" s="17">
-        <v>15</v>
-      </c>
+      <c r="AD38" s="17"/>
       <c r="AE38"/>
-      <c r="AF38" s="18">
-        <v>4.5</v>
-      </c>
+      <c r="AF38" s="18"/>
       <c r="AG38" s="19">
         <v>0</v>
       </c>
@@ -10180,7 +9868,7 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0G5PQCR4W</t>
+          <t>B0G9PT9Y3Q</t>
         </is>
       </c>
       <c r="D39" s="12"/>
@@ -10193,23 +9881,23 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Airpher 褥子清洁剂 UV除菌、除螨、病毒 最大18Kpa 强力吸&amp;拍打40800次 500Ws配备 2 个阶段的 HEPA 过滤器,过敏原对策 (16,000 Pa),低模式 (16,000Pa),低模式 (16,000Pa),超声波技术</t>
+          <t>CREATULIZE BOT X1 全自动床清洁机器人 床上用品清洁剂 一键开启 减少麻烦,270nm的UV紫外线杀菌,去除99.99%螨虫和细菌,14AW强力吸力,搭载15,000次的敲击功能,HEPA高性能过滤网,无绳轻松使用 被子、床垫、沙发、</t>
         </is>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G5PQCR4W?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G9PT9Y3Q?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71Bp3OKbP4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51Bg1dnvSyL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0G5PQCR4W</t>
+          <t>B0G9PT9Y3Q</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10230,11 +9918,11 @@
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="17">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG39" s="19">
         <v>0</v>
@@ -10286,7 +9974,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0G8CZQYDB</t>
+          <t>B0GQ7VMNXJ</t>
         </is>
       </c>
       <c r="D40" s="12"/>
@@ -10299,23 +9987,23 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>被褥清洁剂 大功率 防螨 宽头 拍打 约14000次/分钟 FCA-22H-C 象牙色</t>
+          <t>MOVA 除螨仪 D10 Ultra 被褥清洁器 14000Pa 强力吸力 48000次/分钟高速拍打 UV除菌 超声波 螨虫死灭 65℃温风 5级过滤网 智能螨检测传感器 防止头发缠绕 双层防尘杯 1.89kg轻量 易于保养 防花粉/过敏原 白色</t>
         </is>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GQ7VMNXJ?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/716al-Wu6vL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0G8CZQYDB</t>
+          <t>B0GQ7VMNXJ</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10335,9 +10023,13 @@
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
-      <c r="AD40" s="17"/>
+      <c r="AD40" s="17">
+        <v>10</v>
+      </c>
       <c r="AE40"/>
-      <c r="AF40" s="18"/>
+      <c r="AF40" s="18">
+        <v>4.6</v>
+      </c>
       <c r="AG40" s="19">
         <v>0</v>
       </c>
@@ -10388,7 +10080,7 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0G9PT9Y3Q</t>
+          <t>B0GTTTTP71</t>
         </is>
       </c>
       <c r="D41" s="12"/>
@@ -10401,23 +10093,23 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>CREATULIZE BOT X1 全自动床清洁机器人 床上用品清洁剂 一键开启 减少麻烦,270nm的UV紫外线杀菌,去除99.99%螨虫和细菌,14AW强力吸力,搭载15,000次的敲击功能,HEPA高性能过滤网,无绳轻松使用 被子、床垫、沙发、</t>
+          <t>被褥清洁剂 榻榻米次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A3-W</t>
         </is>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G9PT9Y3Q?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51Bg1dnvSyL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41t94rJieZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0G9PT9Y3Q</t>
+          <t>B0GTTTTP71</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10437,13 +10129,9 @@
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
-      <c r="AD41" s="17">
-        <v>17</v>
-      </c>
+      <c r="AD41" s="17"/>
       <c r="AE41"/>
-      <c r="AF41" s="18">
-        <v>4.3</v>
-      </c>
+      <c r="AF41" s="18"/>
       <c r="AG41" s="19">
         <v>0</v>
       </c>
@@ -10494,7 +10182,7 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0GC542DKX</t>
+          <t>B0GYQWLVBF</t>
         </is>
       </c>
       <c r="D42" s="12"/>
@@ -10507,23 +10195,23 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>[Joejoier] 集尘清洁箱 多功能吸附盒 强力 小型吸尘器 迷你 24小时自动吸附灰尘 快速去除灰尘 健康呼吸 宝宝也可放心使用 时间短 &amp; 省力 Multi Functional Air Magic Box 只需这一台即可轻松打扫 汽车 办公</t>
+          <t>ＯＮＥＳＵＧＡＲ 布団クリーナー 布団掃除機 レイコップ クリーナー ポータブル ワイヤレス 家庭用ダニ除去機 小型軽量、ミニ掃除機 (B) [並行輸入品]</t>
         </is>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GC542DKX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GYQWLVBF?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71FatVxfI2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61GUgngXotL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0GC542DKX</t>
+          <t>B0GYQWLVBF</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10543,13 +10231,9 @@
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
-      <c r="AD42" s="17">
-        <v>8</v>
-      </c>
+      <c r="AD42" s="17"/>
       <c r="AE42"/>
-      <c r="AF42" s="18">
-        <v>1.9</v>
-      </c>
+      <c r="AF42" s="18"/>
       <c r="AG42" s="19">
         <v>0</v>
       </c>
@@ -10600,7 +10284,7 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0GFMWDXRK</t>
+          <t>B0H5P3R6KQ</t>
         </is>
       </c>
       <c r="D43" s="12"/>
@@ -10613,23 +10297,23 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>JUELREOU【除尘消除】集尘清洁箱【2026最新】 强力 24小时自动吸附灰尘 快速去除灰尘 健康呼吸 宝宝也可放心使用 Multi Functional Air Magic Box 汽车 办公室 客厅 卧室 厨房 厕所用 (新版5个)</t>
+          <t>uwant 被子吸尘器 超轻量1.15千克 14kPa强力吸力 13000次/分高速拍 防螨 UV除菌 65°C暖风 UV-C紫外线 搭载HEPA过滤器 防螨 防止毛发缠绕 M80Pro</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GFMWDXRK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H5P3R6KQ?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/617jv+YoAFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71Bs1K02zjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0GFMWDXRK</t>
+          <t>B0H5P3R6KQ</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10650,11 +10334,11 @@
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="17">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="18">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="AG43" s="19">
         <v>0</v>
@@ -10706,7 +10390,7 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0GGHCSSRC</t>
+          <t>B0H6BMMJJ2</t>
         </is>
       </c>
       <c r="D44" s="12"/>
@@ -10719,23 +10403,23 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>2026アップグレード版【ホコリ退治】ダストクリーンボックス 多機能吸着ボックス 置くだけ自動吸塵ボックス 強力 小型掃除機 24時間自動でホコリを吸着 ホコリを素早く除去 健やかな呼吸 赤ちゃんも安心使用 時短 &amp; 省力 Multi Functio</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 充电式纸袋被褥清洁器 白色 FBD-41-W</t>
         </is>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GGHCSSRC?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/7116SveneNL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B0GGHCSSRC</t>
+          <t>B0H6BMMJJ2</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10801,736 +10485,6 @@
       <c r="BQ44" s="20"/>
       <c r="BR44"/>
     </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B0GQ7VMNXJ</t>
-        </is>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45"/>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>MOVA 除螨仪 D10 Ultra 被褥清洁器 14000Pa 强力吸力 48000次/分钟高速拍打 UV除菌 超声波 螨虫死灭 65℃温风 5级过滤网 智能螨检测传感器 防止头发缠绕 双层防尘杯 1.89kg轻量 易于保养 防花粉/过敏原 白色</t>
-        </is>
-      </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GQ7VMNXJ?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/716al-Wu6vL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>B0GQ7VMNXJ</t>
-        </is>
-      </c>
-      <c r="M45" s="1"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="14"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="13"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45"/>
-      <c r="Z45" s="13"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45" s="17">
-        <v>10</v>
-      </c>
-      <c r="AE45"/>
-      <c r="AF45" s="18">
-        <v>4.6</v>
-      </c>
-      <c r="AG45" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH45"/>
-      <c r="AI45" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="1"/>
-      <c r="AL45" s="17"/>
-      <c r="AM45"/>
-      <c r="AN45" s="11"/>
-      <c r="AO45" s="11"/>
-      <c r="AP45"/>
-      <c r="AQ45" s="17"/>
-      <c r="AR45"/>
-      <c r="AS45"/>
-      <c r="AT45"/>
-      <c r="AU45" s="11"/>
-      <c r="AV45" s="12"/>
-      <c r="AW45" s="11"/>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11"/>
-      <c r="BD45" s="11"/>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11"/>
-      <c r="BG45" s="11"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45"/>
-      <c r="BJ45"/>
-      <c r="BK45" s="20"/>
-      <c r="BL45"/>
-      <c r="BM45" s="20"/>
-      <c r="BN45"/>
-      <c r="BO45" s="20"/>
-      <c r="BP45"/>
-      <c r="BQ45" s="20"/>
-      <c r="BR45"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>B0GTTTTP71</t>
-        </is>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46"/>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>被褥清洁剂 榻榻米次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A3-W</t>
-        </is>
-      </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41t94rJieZL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>B0GTTTTP71</t>
-        </is>
-      </c>
-      <c r="M46" s="1"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="13"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46"/>
-      <c r="AB46"/>
-      <c r="AC46"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH46"/>
-      <c r="AI46" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="1"/>
-      <c r="AL46" s="17"/>
-      <c r="AM46"/>
-      <c r="AN46" s="11"/>
-      <c r="AO46" s="11"/>
-      <c r="AP46"/>
-      <c r="AQ46" s="17"/>
-      <c r="AR46"/>
-      <c r="AS46"/>
-      <c r="AT46"/>
-      <c r="AU46" s="11"/>
-      <c r="AV46" s="12"/>
-      <c r="AW46" s="11"/>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11"/>
-      <c r="BD46" s="11"/>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11"/>
-      <c r="BG46" s="11"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46"/>
-      <c r="BJ46"/>
-      <c r="BK46" s="20"/>
-      <c r="BL46"/>
-      <c r="BM46" s="20"/>
-      <c r="BN46"/>
-      <c r="BO46" s="20"/>
-      <c r="BP46"/>
-      <c r="BQ46" s="20"/>
-      <c r="BR46"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>B0GYQWLVBF</t>
-        </is>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47"/>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>ＯＮＥＳＵＧＡＲ 布団クリーナー 布団掃除機 レイコップ クリーナー ポータブル ワイヤレス 家庭用ダニ除去機 小型軽量、ミニ掃除機 (B) [並行輸入品]</t>
-        </is>
-      </c>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GYQWLVBF?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61GUgngXotL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>B0GYQWLVBF</t>
-        </is>
-      </c>
-      <c r="M47" s="1"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="13"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47"/>
-      <c r="AB47"/>
-      <c r="AC47"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH47"/>
-      <c r="AI47" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="1"/>
-      <c r="AL47" s="17"/>
-      <c r="AM47"/>
-      <c r="AN47" s="11"/>
-      <c r="AO47" s="11"/>
-      <c r="AP47"/>
-      <c r="AQ47" s="17"/>
-      <c r="AR47"/>
-      <c r="AS47"/>
-      <c r="AT47"/>
-      <c r="AU47" s="11"/>
-      <c r="AV47" s="12"/>
-      <c r="AW47" s="11"/>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="11"/>
-      <c r="BB47" s="11"/>
-      <c r="BC47" s="11"/>
-      <c r="BD47" s="11"/>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11"/>
-      <c r="BG47" s="11"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47"/>
-      <c r="BJ47"/>
-      <c r="BK47" s="20"/>
-      <c r="BL47"/>
-      <c r="BM47" s="20"/>
-      <c r="BN47"/>
-      <c r="BO47" s="20"/>
-      <c r="BP47"/>
-      <c r="BQ47" s="20"/>
-      <c r="BR47"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0H5P3R6KQ</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48"/>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>uwant 被子吸尘器 超轻量1.15千克 14kPa强力吸力 13000次/分高速拍 防螨 UV除菌 65°C暖风 UV-C紫外线 搭载HEPA过滤器 防螨 防止毛发缠绕 M80Pro</t>
-        </is>
-      </c>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H5P3R6KQ?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71Bs1K02zjL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0H5P3R6KQ</t>
-        </is>
-      </c>
-      <c r="M48" s="1"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48"/>
-      <c r="AD48" s="17">
-        <v>40</v>
-      </c>
-      <c r="AE48"/>
-      <c r="AF48" s="18">
-        <v>4.8</v>
-      </c>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48"/>
-      <c r="AI48" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="1"/>
-      <c r="AL48" s="17"/>
-      <c r="AM48"/>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48"/>
-      <c r="AQ48" s="17"/>
-      <c r="AR48"/>
-      <c r="AS48"/>
-      <c r="AT48"/>
-      <c r="AU48" s="11"/>
-      <c r="AV48" s="12"/>
-      <c r="AW48" s="11"/>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48"/>
-      <c r="BJ48"/>
-      <c r="BK48" s="20"/>
-      <c r="BL48"/>
-      <c r="BM48" s="20"/>
-      <c r="BN48"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>B0H6BMMJJ2</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49"/>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 充电式纸袋被褥清洁器 白色 FBD-41-W</t>
-        </is>
-      </c>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>B0H6BMMJJ2</t>
-        </is>
-      </c>
-      <c r="M49" s="1"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="15"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH49"/>
-      <c r="AI49" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="1"/>
-      <c r="AL49" s="17"/>
-      <c r="AM49"/>
-      <c r="AN49" s="11"/>
-      <c r="AO49" s="11"/>
-      <c r="AP49"/>
-      <c r="AQ49" s="17"/>
-      <c r="AR49"/>
-      <c r="AS49"/>
-      <c r="AT49"/>
-      <c r="AU49" s="11"/>
-      <c r="AV49" s="12"/>
-      <c r="AW49" s="11"/>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11"/>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49"/>
-      <c r="BJ49"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0H6FF5LHZ</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50"/>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>尘箱【除霉真神】超强吸霉全天候清洁净化器【除尘】强力 多功能 24小时自动吸附灰尘 大容量 省时打扫健康呼吸空间 家庭 客厅 卧室 厨房 托儿所 宠物区适用 (6)</t>
-        </is>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H6FF5LHZ?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/711Q4UmnGjL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0H6FF5LHZ</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="18">
-        <v>5</v>
-      </c>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="17"/>
-      <c r="AM50"/>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="17"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="20"/>
-      <c r="BL50"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0HJBYQL8G</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>防尘箱【除灰尘】多功能除尘箱【房屋灰尘的救星】 汽车 办公室 客厅 卧室 厨房 厕所用sMulti Functional Air Magic Box 只需放置即可自动吸尘强力小型吸尘器,迷你,24 小时自动吸附灰尘,快速去除灰尘,健康呼吸,对宝宝</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HJBYQL8G?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71z88krs4mL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0HJBYQL8G</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="18">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -11540,253 +10494,218 @@
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.co.jp/dp/B016HFD82S?psc=1"/>
     <hyperlink ref="K2" r:id="rId4" tooltip="https://images-fe.ssl-images-amazon.com/images/I/4197tvgiQtL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.co.jp/dp/B016HFD82S"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.co.jp/dp/B016UAX3VQ"/>
+    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
     <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.co.jp/dp/B016UAX3VQ?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51CMS9l84gL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.co.jp/dp/B016UAX3VQ"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
+    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY?psc=1"/>
+    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61dODBedyYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61dODBedyYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51kQ4uomOdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.co.jp/dp/B07H4MYMP9"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51kQ4uomOdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.co.jp/dp/B07H4MYMP9"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.co.jp/dp/B07H4MYMP9?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41W46tl8-UL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.co.jp/dp/B07H4MYMP9"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.co.jp/dp/B07H4MYMP9?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41W46tl8-UL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.co.jp/dp/B07H4MYMP9"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71xsLoIIE2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.jp/dp/B0BBVFX2GR"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71xsLoIIE2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.jp/dp/B0BBVFX2GR"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.jp/dp/B0BBVFX2GR?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41yNLrDa+RL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.jp/dp/B0BBVFX2GR"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.jp/dp/B0BCDMQGQ9"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.jp/dp/B0BBVFX2GR?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41yNLrDa+RL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.jp/dp/B0BBVFX2GR"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.jp/dp/B0BCDMQGQ9"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.jp/dp/B0BCDMQGQ9?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41hvEdYzqRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.jp/dp/B0BCDMQGQ9"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.jp/dp/B0BCDMQGQ9?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41hvEdYzqRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.jp/dp/B0BCDMQGQ9"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.jp/dp/B0CZN7FLSN"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.jp/dp/B0CZN7FLSN"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.jp/dp/B0CZN7FLSN?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61gx54pmm0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.jp/dp/B0CZN7FLSN"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.jp/dp/B0CZN7FLSN?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61gx54pmm0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.jp/dp/B0CZN7FLSN"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-fe.ssl-images-amazon.com/images/I/81kvopazcOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.co.jp/dp/B0D7C6VH4G"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-fe.ssl-images-amazon.com/images/I/81kvopazcOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.co.jp/dp/B0D7C6VH4G"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.co.jp/dp/B0D7C6VH4G?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71b-Rog4TuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.co.jp/dp/B0D7C6VH4G"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.co.jp/dp/B0D7C6VH4G?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71b-Rog4TuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.co.jp/dp/B0D7C6VH4G"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-fe.ssl-images-amazon.com/images/I/6147nu3B4yL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-fe.ssl-images-amazon.com/images/I/6147nu3B4yL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.jp/dp/B0DJ84X2K4"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.jp/dp/B0DJ84X2K4"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.jp/dp/B0DJ84X2K4?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61lNaH-6QjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.jp/dp/B0DJ84X2K4"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.jp/dp/B0DJ8MNLKW"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.jp/dp/B0DJ84X2K4?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61lNaH-6QjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.jp/dp/B0DJ84X2K4"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.jp/dp/B0DJ8MNLKW"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.jp/dp/B0DJ8MNLKW?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61hr6UbLVxL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.jp/dp/B0DJ8MNLKW"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.jp/dp/B0DP629CCF"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.jp/dp/B0DJ8MNLKW?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61hr6UbLVxL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.jp/dp/B0DJ8MNLKW"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.jp/dp/B0DP629CCF"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.jp/dp/B0DP629CCF?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61YqmCRO62L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.jp/dp/B0DP629CCF"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.jp/dp/B0DQPZRS8L"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.jp/dp/B0DP629CCF?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61YqmCRO62L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.jp/dp/B0DP629CCF"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B0DQPZRS8L"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.jp/dp/B0DQPZRS8L?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-fe.ssl-images-amazon.com/images/I/612s3TGcUVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.jp/dp/B0DQPZRS8L"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B0DQPZRS8L?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-fe.ssl-images-amazon.com/images/I/612s3TGcUVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B0DQPZRS8L"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.jp/dp/B0DSVXKTTZ"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0DSVXKTTZ"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.jp/dp/B0DSVXKTTZ?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-fe.ssl-images-amazon.com/images/I/715CyXTopOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.jp/dp/B0DSVXKTTZ"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0DSVXKTTZ?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-fe.ssl-images-amazon.com/images/I/715CyXTopOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.jp/dp/B0DSVXKTTZ"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71332p8jV1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.jp/dp/B0DZCG5HCH"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71332p8jV1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.jp/dp/B0DZCG5HCH?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71hIr36PswL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.jp/dp/B0DZCG5HCH"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B0F2MJH8GH"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31dizVJn3lL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.jp/dp/B0DZCG5HCH"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.jp/dp/B0F2MJH8GH?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71Gz6T9kaVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B0F2MJH8GH"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.jp/dp/B0F2MLKF9S"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.jp/dp/B0DZCG5HCH?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71hIr36PswL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.jp/dp/B0DZCG5HCH"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.jp/dp/B0F2MJH8GH"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.jp/dp/B0F2MLKF9S?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-fe.ssl-images-amazon.com/images/I/7194c3NEgeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.jp/dp/B0F2MLKF9S"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.jp/dp/B0F2MJH8GH?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71Gz6T9kaVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.jp/dp/B0F2MJH8GH"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.jp/dp/B0F2MLKF9S"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.jp/dp/B0FB3663JX"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.jp/dp/B0F2MLKF9S?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-fe.ssl-images-amazon.com/images/I/7194c3NEgeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.jp/dp/B0F2MLKF9S"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.jp/dp/B0FB3663JX?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51kxnq4fNYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.jp/dp/B0FB3663JX"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.jp/dp/B0FCBS5DCM"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.jp/dp/B0FB3663JX"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.jp/dp/B0FCBS5DCM?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71sM4fI8XJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.jp/dp/B0FCBS5DCM"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.jp/dp/B0FR16C82Q"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.jp/dp/B0FB3663JX?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51kxnq4fNYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.jp/dp/B0FB3663JX"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.jp/dp/B0FCBS5DCM"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.jp/dp/B0FR16C82Q?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51dSYaVLTcL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.jp/dp/B0FR16C82Q"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.jp/dp/B0FR467QTB"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.jp/dp/B0FCBS5DCM?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71sM4fI8XJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.jp/dp/B0FCBS5DCM"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.jp/dp/B0FR16C82Q"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.jp/dp/B0FR467QTB?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31KvYyBRXvL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.jp/dp/B0FR467QTB"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.jp/dp/B0FWBY3CVW"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.jp/dp/B0FR16C82Q?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51dSYaVLTcL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.jp/dp/B0FR16C82Q"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.jp/dp/B0FR467QTB"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.jp/dp/B0FWBY3CVW?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71d9mh-B3OL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.jp/dp/B0FWBY3CVW"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.jp/dp/B0G1C3LTTM"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.jp/dp/B0FR467QTB?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31KvYyBRXvL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0FR467QTB"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B0FWBY3CVW"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.jp/dp/B0G1C3LTTM?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51MPPMKoAmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0G1C3LTTM"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B0G5PQCR4W"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B0FWBY3CVW?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71d9mh-B3OL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.jp/dp/B0FWBY3CVW"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.jp/dp/B0G1C3LTTM"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B0G5PQCR4W?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71Bp3OKbP4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.jp/dp/B0G5PQCR4W"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B0G1C3LTTM?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51MPPMKoAmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B0G1C3LTTM"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B0G5PQCR4W"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B0G9PT9Y3Q"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B0G5PQCR4W?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71Bp3OKbP4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.jp/dp/B0G5PQCR4W"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B0G9PT9Y3Q?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51Bg1dnvSyL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.jp/dp/B0G9PT9Y3Q"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.jp/dp/B0GQ7VMNXJ"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B0G9PT9Y3Q"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.jp/dp/B0GQ7VMNXJ?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-fe.ssl-images-amazon.com/images/I/716al-Wu6vL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.jp/dp/B0GQ7VMNXJ"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.jp/dp/B0G9PT9Y3Q?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51Bg1dnvSyL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0G9PT9Y3Q"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B0GC542DKX"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41t94rJieZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B0GYQWLVBF"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B0GC542DKX?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71FatVxfI2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.jp/dp/B0GC542DKX"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0GFMWDXRK"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B0GYQWLVBF?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61GUgngXotL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.jp/dp/B0GYQWLVBF"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0H5P3R6KQ"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0GFMWDXRK?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-fe.ssl-images-amazon.com/images/I/617jv+YoAFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0GFMWDXRK"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0GGHCSSRC"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0H5P3R6KQ?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71Bs1K02zjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0H5P3R6KQ"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B0GGHCSSRC?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-fe.ssl-images-amazon.com/images/I/7116SveneNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0GGHCSSRC"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0GQ7VMNXJ"/>
-    <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0GQ7VMNXJ?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-fe.ssl-images-amazon.com/images/I/716al-Wu6vL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0GQ7VMNXJ"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
-    <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41t94rJieZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B0GYQWLVBF"/>
-    <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0GYQWLVBF?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61GUgngXotL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0GYQWLVBF"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B0H5P3R6KQ"/>
-    <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B0H5P3R6KQ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71Bs1K02zjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.jp/dp/B0H5P3R6KQ"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
-    <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0H6FF5LHZ"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0H6FF5LHZ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/711Q4UmnGjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0H6FF5LHZ"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0HJBYQL8G"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0HJBYQL8G?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71z88krs4mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0HJBYQL8G"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-fe.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId216"/>
 </worksheet>
 </file>
 
